--- a/artfynd/A 25279-2025 artfynd.xlsx
+++ b/artfynd/A 25279-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,6 +1017,312 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126348488</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>St Tuvbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500313</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6996224</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126348487</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>St Tuvbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500307</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6996204</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126348486</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>St Tuvbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500106</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6996222</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25279-2025 artfynd.xlsx
+++ b/artfynd/A 25279-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>126348488</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>126348487</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126348486</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 25279-2025 artfynd.xlsx
+++ b/artfynd/A 25279-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>126348488</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>126348487</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126348486</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 25279-2025 artfynd.xlsx
+++ b/artfynd/A 25279-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>126348488</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>126348487</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126348486</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 25279-2025 artfynd.xlsx
+++ b/artfynd/A 25279-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>126348488</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>126348487</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126348486</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 25279-2025 artfynd.xlsx
+++ b/artfynd/A 25279-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>126348488</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>126348487</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126348486</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
